--- a/data/trans_dic/LAWTONB_2R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody)</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,14; 33,2</t>
+          <t>24,49; 33,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,41; 35,82</t>
+          <t>26,41; 36,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,1; 31,84</t>
+          <t>23,06; 32,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,24; 43,41</t>
+          <t>33,77; 43,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,71; 39,7</t>
+          <t>31,43; 39,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,89; 44,69</t>
+          <t>36,83; 44,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,47; 43,1</t>
+          <t>34,58; 43,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,01; 56,44</t>
+          <t>49,97; 56,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,92; 36,1</t>
+          <t>30,12; 35,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,45; 39,94</t>
+          <t>33,82; 40,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,02; 37,43</t>
+          <t>31,21; 37,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,11; 50,53</t>
+          <t>45,28; 50,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,1; 25,98</t>
+          <t>9,81; 25,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,69; 25,53</t>
+          <t>10,52; 26,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,02; 16,59</t>
+          <t>8,07; 17,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,01; 20,39</t>
+          <t>13,1; 20,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,23; 36,31</t>
+          <t>12,17; 33,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,95; 35,5</t>
+          <t>15,51; 36,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,56; 37,36</t>
+          <t>21,8; 37,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 24,72</t>
+          <t>4,67; 24,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,37; 26,33</t>
+          <t>12,52; 25,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14,36; 26,76</t>
+          <t>15,09; 27,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,41; 25,3</t>
+          <t>16,44; 25,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 20,72</t>
+          <t>6,4; 20,76</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 44,11</t>
+          <t>13,43; 45,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,7</t>
+          <t>0,0; 26,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 26,27</t>
+          <t>4,55; 26,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,9; 21,37</t>
+          <t>9,7; 21,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,4; 61,55</t>
+          <t>23,57; 61,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 42,58</t>
+          <t>5,15; 43,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 45,71</t>
+          <t>10,3; 45,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,96; 27,89</t>
+          <t>14,85; 28,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,1; 45,38</t>
+          <t>21,82; 47,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,65; 27,04</t>
+          <t>4,71; 26,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 30,77</t>
+          <t>9,0; 29,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,37; 22,05</t>
+          <t>13,6; 22,0</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,83; 30,2</t>
+          <t>22,92; 30,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,08; 31,0</t>
+          <t>22,81; 30,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,24; 24,59</t>
+          <t>17,84; 24,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,63; 28,0</t>
+          <t>22,3; 28,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,72; 38,03</t>
+          <t>31,02; 38,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,93; 42,34</t>
+          <t>34,8; 42,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,76; 39,57</t>
+          <t>32,33; 39,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,38; 42,31</t>
+          <t>17,92; 41,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,02; 33,51</t>
+          <t>28,22; 33,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,68; 36,0</t>
+          <t>30,79; 36,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,87; 32,17</t>
+          <t>26,96; 32,05</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,67; 34,91</t>
+          <t>17,64; 34,77</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody)</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90103; 123907</t>
+          <t>91382; 123348</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109426; 148457</t>
+          <t>109437; 151622</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81762; 112689</t>
+          <t>81626; 113258</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88350; 115384</t>
+          <t>89763; 115665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>186384; 233314</t>
+          <t>184704; 231434</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>234104; 283599</t>
+          <t>233728; 285413</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>191227; 239097</t>
+          <t>191830; 240940</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>249012; 281018</t>
+          <t>248819; 279511</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287480; 346933</t>
+          <t>289419; 345336</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>350902; 418897</t>
+          <t>354703; 419563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>281903; 340091</t>
+          <t>283578; 341357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>344540; 385888</t>
+          <t>345790; 388446</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8893; 22884</t>
+          <t>8644; 22808</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12689; 30299</t>
+          <t>12488; 31090</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15432; 31942</t>
+          <t>15546; 33564</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35477; 55591</t>
+          <t>35703; 54585</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7611; 22589</t>
+          <t>7573; 21135</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13254; 29495</t>
+          <t>12887; 30548</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42423; 70263</t>
+          <t>41002; 70605</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18546; 112219</t>
+          <t>21185; 112528</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18588; 39565</t>
+          <t>18822; 38390</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28962; 53991</t>
+          <t>30436; 54568</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62448; 96297</t>
+          <t>62575; 96089</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>45437; 150589</t>
+          <t>46521; 150860</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5665; 18171</t>
+          <t>5532; 18865</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6831</t>
+          <t>0; 7041</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1895; 11042</t>
+          <t>1914; 11267</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10217; 22060</t>
+          <t>10018; 22010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6290; 16546</t>
+          <t>6335; 16420</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1087; 9472</t>
+          <t>1145; 9583</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3134; 15393</t>
+          <t>3470; 15229</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9956; 19894</t>
+          <t>10593; 20078</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14364; 30893</t>
+          <t>14857; 32648</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2272; 13199</t>
+          <t>2301; 12730</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7396; 23297</t>
+          <t>6814; 22204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23346; 38496</t>
+          <t>23747; 38414</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>114697; 151761</t>
+          <t>115143; 152959</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>129139; 173471</t>
+          <t>127667; 172407</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>107307; 144677</t>
+          <t>105007; 141517</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>145226; 179702</t>
+          <t>143107; 179973</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>207894; 257407</t>
+          <t>209951; 260274</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>258432; 313226</t>
+          <t>257460; 313589</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>246635; 307270</t>
+          <t>251020; 305776</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>177879; 432959</t>
+          <t>183313; 429703</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>330432; 395194</t>
+          <t>332744; 395723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>398734; 467848</t>
+          <t>400061; 470054</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>366790; 439137</t>
+          <t>368057; 437509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>327415; 581149</t>
+          <t>293631; 578944</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/LAWTONB_2R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/LAWTONB_2R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,49; 33,05</t>
+          <t>24,36; 33,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,41; 36,59</t>
+          <t>26,4; 35,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,06; 32,0</t>
+          <t>22,94; 31,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33,77; 43,51</t>
+          <t>33,07; 42,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,43; 39,38</t>
+          <t>31,61; 39,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,83; 44,98</t>
+          <t>36,48; 44,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,58; 43,43</t>
+          <t>34,34; 43,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49,97; 56,14</t>
+          <t>49,59; 56,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,12; 35,94</t>
+          <t>29,85; 35,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33,82; 40,0</t>
+          <t>33,7; 40,05</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,21; 37,57</t>
+          <t>31,02; 37,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,28; 50,86</t>
+          <t>44,99; 50,32</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,81; 25,89</t>
+          <t>9,79; 24,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,52; 26,2</t>
+          <t>10,76; 25,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,07; 17,43</t>
+          <t>7,92; 16,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,1; 20,02</t>
+          <t>13,28; 20,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,17; 33,97</t>
+          <t>11,95; 35,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,51; 36,77</t>
+          <t>16,68; 37,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,8; 37,54</t>
+          <t>22,01; 37,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,67; 24,78</t>
+          <t>21,01; 28,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 25,54</t>
+          <t>12,78; 25,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,09; 27,05</t>
+          <t>14,68; 26,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,44; 25,25</t>
+          <t>16,18; 25,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,4; 20,76</t>
+          <t>17,59; 22,99</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,43; 45,8</t>
+          <t>13,33; 45,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,49</t>
+          <t>0,0; 24,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 26,81</t>
+          <t>4,16; 27,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 21,32</t>
+          <t>9,44; 20,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,57; 61,09</t>
+          <t>25,43; 62,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 43,08</t>
+          <t>5,14; 45,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,3; 45,23</t>
+          <t>9,82; 48,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,85; 28,15</t>
+          <t>14,7; 28,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21,82; 47,96</t>
+          <t>20,78; 46,06</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 26,07</t>
+          <t>5,92; 26,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 29,33</t>
+          <t>8,61; 28,72</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,6; 22,0</t>
+          <t>12,98; 21,58</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,92; 30,44</t>
+          <t>22,74; 30,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,81; 30,81</t>
+          <t>22,85; 30,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,84; 24,05</t>
+          <t>18,13; 24,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,3; 28,05</t>
+          <t>22,02; 27,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,02; 38,45</t>
+          <t>30,92; 38,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,8; 42,38</t>
+          <t>34,66; 42,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,33; 39,38</t>
+          <t>32,14; 39,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,92; 41,99</t>
+          <t>38,82; 43,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,22; 33,56</t>
+          <t>28,38; 33,46</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30,79; 36,17</t>
+          <t>30,66; 36,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26,96; 32,05</t>
+          <t>26,95; 32,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,64; 34,77</t>
+          <t>32,17; 35,98</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101533</t>
+          <t>107923</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>264671</t>
+          <t>284413</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>366204</t>
+          <t>392336</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>91382; 123348</t>
+          <t>90908; 125025</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109437; 151622</t>
+          <t>109407; 148160</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81626; 113258</t>
+          <t>81199; 112061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89763; 115665</t>
+          <t>94706; 122625</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>184704; 231434</t>
+          <t>185792; 232506</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>233728; 285413</t>
+          <t>231498; 281244</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>191830; 240940</t>
+          <t>190508; 240621</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>248819; 279511</t>
+          <t>265594; 300823</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289419; 345336</t>
+          <t>286879; 343583</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>354703; 419563</t>
+          <t>353528; 420106</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>283578; 341357</t>
+          <t>281857; 339199</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>345790; 388446</t>
+          <t>369786; 413606</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44985</t>
+          <t>49507</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>59339</t>
+          <t>67532</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>104324</t>
+          <t>117039</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8644; 22808</t>
+          <t>8620; 21732</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12488; 31090</t>
+          <t>12766; 30324</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15546; 33564</t>
+          <t>15254; 32682</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35703; 54585</t>
+          <t>40265; 61203</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7573; 21135</t>
+          <t>7435; 21801</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12887; 30548</t>
+          <t>13856; 30815</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41002; 70605</t>
+          <t>41398; 70343</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21185; 112528</t>
+          <t>57914; 79002</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18822; 38390</t>
+          <t>19211; 37956</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30436; 54568</t>
+          <t>29610; 53600</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62575; 96089</t>
+          <t>61589; 95329</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>46521; 150860</t>
+          <t>101843; 133077</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30156</t>
+          <t>33359</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5532; 18865</t>
+          <t>5491; 18572</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 7041</t>
+          <t>0; 6634</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1914; 11267</t>
+          <t>1749; 11680</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10018; 22010</t>
+          <t>11058; 24365</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6335; 16420</t>
+          <t>6837; 16690</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1145; 9583</t>
+          <t>1144; 10157</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3470; 15229</t>
+          <t>3306; 16170</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10593; 20078</t>
+          <t>12181; 23317</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14857; 32648</t>
+          <t>14145; 31353</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2301; 12730</t>
+          <t>2892; 12778</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6814; 22204</t>
+          <t>6519; 21740</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23747; 38414</t>
+          <t>25954; 43164</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161726</t>
+          <t>174002</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>338959</t>
+          <t>368731</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>500685</t>
+          <t>542733</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>115143; 152959</t>
+          <t>114256; 153418</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>127667; 172407</t>
+          <t>127896; 172620</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>105007; 141517</t>
+          <t>106689; 143380</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143107; 179973</t>
+          <t>155566; 193700</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>209951; 260274</t>
+          <t>209277; 259970</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>257460; 313589</t>
+          <t>256436; 310887</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>251020; 305776</t>
+          <t>249585; 306789</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>183313; 429703</t>
+          <t>347117; 391273</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>332744; 395723</t>
+          <t>334693; 394645</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>400061; 470054</t>
+          <t>398452; 468147</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>368057; 437509</t>
+          <t>367890; 437218</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>293631; 578944</t>
+          <t>514989; 575924</t>
         </is>
       </c>
     </row>
